--- a/DesignData/ModConfig.xlsx
+++ b/DesignData/ModConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="46">
   <si>
     <t>ItemType</t>
   </si>
@@ -44,6 +44,12 @@
     <t>EntryOp</t>
   </si>
   <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
     <t>enum:ItemTypeEnum</t>
   </si>
   <si>
@@ -59,6 +65,9 @@
     <t>enum:ModOp</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>Mod_Damage</t>
   </si>
   <si>
@@ -68,16 +77,34 @@
     <t>BulletDamage</t>
   </si>
   <si>
+    <t>Mul</t>
+  </si>
+  <si>
+    <t>伤害芯片</t>
+  </si>
+  <si>
+    <t>提升武器伤害</t>
+  </si>
+  <si>
+    <t>SpreadAngle</t>
+  </si>
+  <si>
+    <t>Mod_Rpm</t>
+  </si>
+  <si>
+    <t>Rpm</t>
+  </si>
+  <si>
     <t>Add</t>
   </si>
   <si>
-    <t>Mod_Rpm</t>
-  </si>
-  <si>
-    <t>Rpm</t>
-  </si>
-  <si>
-    <t>Mul</t>
+    <t>射速芯片</t>
+  </si>
+  <si>
+    <t>提升武器射速</t>
+  </si>
+  <si>
+    <t>ReloadTime</t>
   </si>
   <si>
     <t>Mod_Homing</t>
@@ -89,10 +116,55 @@
     <t>Set</t>
   </si>
   <si>
+    <t>追踪芯片</t>
+  </si>
+  <si>
+    <t>子弹自动追踪敌人</t>
+  </si>
+  <si>
     <t>BulletSpeed</t>
   </si>
   <si>
-    <t>SpreadAngle</t>
+    <t>Mod_Spread</t>
+  </si>
+  <si>
+    <t>稳定芯片</t>
+  </si>
+  <si>
+    <t>减少武器散射</t>
+  </si>
+  <si>
+    <t>Mod_Penetration</t>
+  </si>
+  <si>
+    <t>Penetration</t>
+  </si>
+  <si>
+    <t>穿透芯片</t>
+  </si>
+  <si>
+    <t>子弹穿透敌人</t>
+  </si>
+  <si>
+    <t>Mod_Ammo</t>
+  </si>
+  <si>
+    <t>MaxMagazine</t>
+  </si>
+  <si>
+    <t>扩容芯片</t>
+  </si>
+  <si>
+    <t>增加弹匣容量</t>
+  </si>
+  <si>
+    <t>Mod_Reload</t>
+  </si>
+  <si>
+    <t>装填芯片</t>
+  </si>
+  <si>
+    <t>加快换弹速度</t>
   </si>
 </sst>
 </file>
@@ -105,14 +177,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -568,148 +633,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1061,17 +1126,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="4"/>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="18.875" customWidth="1"/>
     <col min="2" max="2" width="21.125" customWidth="1"/>
     <col min="3" max="3" width="18.375" customWidth="1"/>
     <col min="4" max="4" width="12.5" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
+    <col min="6" max="6" width="18.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1087,107 +1153,402 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D4">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D6">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="E6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8">
+        <v>-0.3</v>
+      </c>
+      <c r="E8" t="s">
         <v>16</v>
+      </c>
+      <c r="F8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10">
+        <v>-2</v>
+      </c>
+      <c r="E10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11">
+        <v>-0.3</v>
+      </c>
+      <c r="E11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13">
+        <v>0.1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14">
+        <v>0.1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15">
+        <v>0.4</v>
+      </c>
+      <c r="E15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16">
+        <v>0.1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17">
+        <v>-0.25</v>
+      </c>
+      <c r="E17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" t="s">
+        <v>44</v>
+      </c>
+      <c r="G17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18">
+        <v>-0.1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
